--- a/batchstudent/Results/AnhDThe187386/TC6/GradeDetail.xlsx
+++ b/batchstudent/Results/AnhDThe187386/TC6/GradeDetail.xlsx
@@ -164,24 +164,33 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN_SENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Connection established</x:t>
   </x:si>
   <x:si>
+    <x:t>ESTABLISHED</x:t>
+  </x:si>
+  <x:si>
     <x:t>PSH, ACK</x:t>
   </x:si>
   <x:si>
@@ -192,6 +201,39 @@
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN_RECEIVED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 bytes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160 bytes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN_WAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115 bytes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>157 bytes</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -218,7 +260,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -227,7 +269,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -250,7 +302,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -260,8 +312,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -271,6 +329,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -930,11 +996,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R23"/>
+  <x:dimension ref="A1:R82"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -944,7 +1010,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14.139196" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1041,25 +1107,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P2" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>49</x:v>
@@ -1097,7 +1163,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1117,8 +1183,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R3" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1138,10 +1204,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1153,25 +1219,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P4" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="Q4" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>49</x:v>
@@ -1194,10 +1260,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
@@ -1209,7 +1275,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1229,8 +1295,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R5" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1250,10 +1316,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1265,25 +1331,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P6" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>57120</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>49</x:v>
@@ -1306,10 +1372,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
@@ -1321,7 +1387,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1341,8 +1407,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R7" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1362,10 +1428,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1377,25 +1443,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P8" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="Q8" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
         <x:v>49</x:v>
@@ -1418,10 +1484,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,7 +1499,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1453,8 +1519,8 @@
       <x:c r="Q9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R9" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R9" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1474,10 +1540,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1489,25 +1555,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P10" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
+        <x:v>57120</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>49</x:v>
@@ -1530,10 +1596,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1545,7 +1611,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>17</x:v>
@@ -1565,8 +1631,8 @@
       <x:c r="Q11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R11" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R11" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1586,10 +1652,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1601,25 +1667,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P12" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R12" s="2" t="s">
         <x:v>49</x:v>
@@ -1657,25 +1723,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P13" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="Q13" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>49</x:v>
@@ -1713,7 +1779,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
         <x:v>17</x:v>
@@ -1733,8 +1799,8 @@
       <x:c r="Q14" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R14" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R14" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:18">
@@ -1754,10 +1820,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
@@ -1769,25 +1835,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q15" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P15" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="Q15" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>49</x:v>
@@ -1810,10 +1876,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>17</x:v>
@@ -1825,7 +1891,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
         <x:v>17</x:v>
@@ -1845,8 +1911,8 @@
       <x:c r="Q16" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R16" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R16" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:18">
@@ -1866,10 +1932,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
@@ -1881,25 +1947,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q17" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P17" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q17" s="0">
+        <x:v>56526</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>49</x:v>
@@ -1922,10 +1988,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>17</x:v>
@@ -1937,7 +2003,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
         <x:v>17</x:v>
@@ -1957,8 +2023,8 @@
       <x:c r="Q18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R18" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R18" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -1978,10 +2044,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
@@ -1993,25 +2059,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P19" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="Q19" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R19" s="2" t="s">
         <x:v>49</x:v>
@@ -2034,10 +2100,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
@@ -2049,7 +2115,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
         <x:v>17</x:v>
@@ -2069,8 +2135,8 @@
       <x:c r="Q20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R20" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R20" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2090,10 +2156,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
@@ -2105,25 +2171,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q21" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P21" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q21" s="0">
+        <x:v>56526</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>49</x:v>
@@ -2146,10 +2212,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
@@ -2161,7 +2227,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>17</x:v>
@@ -2181,8 +2247,8 @@
       <x:c r="Q22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R22" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R22" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2202,43 +2268,3347 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G23" s="0" t="s">
+      <x:c r="L23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
+    </x:row>
+    <x:row r="24" spans="1:18">
+      <x:c r="A24" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M24" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P24" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q24" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="R24" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:18">
+      <x:c r="A25" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L25" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M25" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O25" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P25" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="Q25" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R25" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:18">
+      <x:c r="A26" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M26" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N26" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O26" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P26" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q26" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="R26" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:18">
+      <x:c r="A27" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M27" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P27" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q27" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="R27" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:18">
+      <x:c r="A28" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K28" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M28" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P28" s="0">
+        <x:v>57120</x:v>
+      </x:c>
+      <x:c r="Q28" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R28" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:18">
+      <x:c r="A29" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L29" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R23" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="M29" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P29" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="Q29" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R29" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:18">
+      <x:c r="A30" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L30" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M30" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P30" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q30" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="R30" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:18">
+      <x:c r="A31" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M31" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N31" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O31" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P31" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="Q31" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R31" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:18">
+      <x:c r="A32" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L32" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M32" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P32" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q32" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="R32" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:18">
+      <x:c r="A33" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L33" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M33" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O33" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="P33" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q33" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="R33" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:18">
+      <x:c r="A34" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M34" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N34" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P34" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="Q34" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R34" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:18">
+      <x:c r="A35" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M35" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N35" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P35" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q35" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="R35" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:18">
+      <x:c r="A36" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L36" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M36" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N36" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P36" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="Q36" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R36" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:18">
+      <x:c r="A37" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L37" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M37" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P37" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q37" s="0">
+        <x:v>55232</x:v>
+      </x:c>
+      <x:c r="R37" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:18">
+      <x:c r="A38" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L38" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M38" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N38" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P38" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="Q38" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R38" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:18">
+      <x:c r="A39" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L39" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M39" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N39" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P39" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q39" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="R39" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:18">
+      <x:c r="A40" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L40" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M40" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N40" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P40" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="Q40" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R40" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:18">
+      <x:c r="A41" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L41" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M41" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O41" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P41" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="Q41" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R41" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:18">
+      <x:c r="A42" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L42" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M42" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N42" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P42" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q42" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="R42" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:18">
+      <x:c r="A43" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L43" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M43" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O43" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="P43" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q43" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="R43" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:18">
+      <x:c r="A44" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L44" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M44" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P44" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="Q44" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R44" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:18">
+      <x:c r="A45" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L45" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M45" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P45" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q45" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="R45" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:18">
+      <x:c r="A46" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K46" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L46" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M46" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N46" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P46" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="Q46" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R46" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:18">
+      <x:c r="A47" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K47" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L47" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M47" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N47" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P47" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q47" s="0">
+        <x:v>33100</x:v>
+      </x:c>
+      <x:c r="R47" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:18">
+      <x:c r="A48" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L48" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M48" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N48" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P48" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="Q48" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R48" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:18">
+      <x:c r="A49" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K49" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L49" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M49" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N49" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P49" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q49" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="R49" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:18">
+      <x:c r="A50" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K50" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L50" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M50" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N50" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P50" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="Q50" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R50" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:18">
+      <x:c r="A51" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K51" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L51" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M51" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N51" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O51" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P51" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="Q51" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R51" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:18">
+      <x:c r="A52" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K52" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L52" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M52" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N52" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P52" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q52" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="R52" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:18">
+      <x:c r="A53" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L53" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M53" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N53" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O53" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P53" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q53" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="R53" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:18">
+      <x:c r="A54" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K54" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L54" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M54" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N54" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P54" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="Q54" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R54" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:18">
+      <x:c r="A55" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K55" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L55" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M55" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N55" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P55" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q55" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="R55" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:18">
+      <x:c r="A56" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L56" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M56" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N56" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P56" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="Q56" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R56" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:18">
+      <x:c r="A57" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K57" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L57" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M57" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N57" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P57" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q57" s="0">
+        <x:v>34802</x:v>
+      </x:c>
+      <x:c r="R57" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:18">
+      <x:c r="A58" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K58" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L58" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M58" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N58" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P58" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="Q58" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R58" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:18">
+      <x:c r="A59" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K59" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L59" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M59" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N59" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P59" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q59" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="R59" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:18">
+      <x:c r="A60" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K60" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L60" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M60" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N60" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P60" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="Q60" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R60" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:18">
+      <x:c r="A61" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L61" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M61" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N61" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O61" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P61" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="Q61" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R61" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:18">
+      <x:c r="A62" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K62" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L62" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M62" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N62" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P62" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q62" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="R62" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:18">
+      <x:c r="A63" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K63" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L63" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M63" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N63" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O63" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="P63" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q63" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="R63" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:18">
+      <x:c r="A64" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L64" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M64" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N64" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P64" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="Q64" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R64" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:18">
+      <x:c r="A65" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L65" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M65" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N65" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P65" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q65" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="R65" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:18">
+      <x:c r="A66" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K66" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L66" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M66" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N66" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P66" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="Q66" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R66" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:18">
+      <x:c r="A67" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K67" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L67" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M67" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N67" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P67" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q67" s="0">
+        <x:v>53310</x:v>
+      </x:c>
+      <x:c r="R67" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:18">
+      <x:c r="A68" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K68" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L68" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M68" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N68" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P68" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="Q68" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R68" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:18">
+      <x:c r="A69" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K69" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L69" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M69" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N69" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P69" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q69" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="R69" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:18">
+      <x:c r="A70" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K70" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L70" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M70" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N70" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P70" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="Q70" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R70" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:18">
+      <x:c r="A71" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K71" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L71" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M71" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N71" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O71" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P71" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="Q71" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R71" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:18">
+      <x:c r="A72" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K72" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L72" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M72" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N72" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P72" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q72" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="R72" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:18">
+      <x:c r="A73" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K73" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L73" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M73" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N73" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O73" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="P73" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q73" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="R73" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:18">
+      <x:c r="A74" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K74" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L74" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M74" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N74" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P74" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="Q74" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R74" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:18">
+      <x:c r="A75" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K75" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L75" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M75" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N75" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P75" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q75" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="R75" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:18">
+      <x:c r="A76" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K76" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L76" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M76" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N76" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P76" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="Q76" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R76" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:18">
+      <x:c r="A77" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K77" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L77" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M77" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N77" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P77" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q77" s="0">
+        <x:v>51448</x:v>
+      </x:c>
+      <x:c r="R77" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:18">
+      <x:c r="A78" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K78" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L78" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M78" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N78" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P78" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q78" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="R78" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:18">
+      <x:c r="A79" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K79" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L79" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M79" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N79" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O79" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="P79" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="Q79" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R79" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:18">
+      <x:c r="A80" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K80" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L80" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M80" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N80" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O80" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="P80" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q80" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="R80" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:18">
+      <x:c r="A81" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K81" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L81" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M81" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N81" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P81" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q81" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="R81" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:18">
+      <x:c r="A82" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K82" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L82" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M82" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N82" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P82" s="0">
+        <x:v>56526</x:v>
+      </x:c>
+      <x:c r="Q82" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R82" s="4" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/batchstudent/Results/AnhDThe187386/TC6/GradeDetail.xlsx
+++ b/batchstudent/Results/AnhDThe187386/TC6/GradeDetail.xlsx
@@ -164,34 +164,79 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN_SENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN_RECEIVED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESTABLISHED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 bytes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160 bytes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN_WAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115 bytes</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection established</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSH, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>157 bytes</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -218,7 +263,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -227,7 +272,22 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -250,7 +310,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -260,8 +320,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -271,6 +340,18 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -930,11 +1011,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R23"/>
+  <x:dimension ref="A1:R72"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -944,7 +1025,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14.139196" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1041,25 +1122,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P2" s="0">
+        <x:v>38134</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>49</x:v>
@@ -1097,25 +1178,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P3" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>38134</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>49</x:v>
@@ -1138,10 +1219,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1153,25 +1234,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P4" s="0">
+        <x:v>38134</x:v>
+      </x:c>
+      <x:c r="Q4" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>49</x:v>
@@ -1194,10 +1275,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
@@ -1209,25 +1290,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P5" s="0">
+        <x:v>38134</x:v>
+      </x:c>
+      <x:c r="Q5" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>49</x:v>
@@ -1250,10 +1331,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1265,25 +1346,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P6" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>38134</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>49</x:v>
@@ -1306,10 +1387,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
@@ -1321,25 +1402,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="P7" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q7" s="0">
+        <x:v>38134</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>49</x:v>
@@ -1362,10 +1443,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1377,25 +1458,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P8" s="0">
+        <x:v>38134</x:v>
+      </x:c>
+      <x:c r="Q8" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
         <x:v>49</x:v>
@@ -1418,10 +1499,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,28 +1514,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R9" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="P9" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q9" s="0">
+        <x:v>38134</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1474,10 +1555,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1489,25 +1570,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P10" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
+        <x:v>38134</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>49</x:v>
@@ -1530,10 +1611,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1545,28 +1626,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R11" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="P11" s="0">
+        <x:v>38134</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1586,10 +1667,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1601,25 +1682,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P12" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R12" s="2" t="s">
         <x:v>49</x:v>
@@ -1657,25 +1738,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P13" s="0">
+        <x:v>47274</x:v>
+      </x:c>
+      <x:c r="Q13" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>49</x:v>
@@ -1713,25 +1794,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O14" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q14" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P14" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q14" s="0">
+        <x:v>47274</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>49</x:v>
@@ -1754,10 +1835,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
@@ -1769,25 +1850,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q15" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P15" s="0">
+        <x:v>47274</x:v>
+      </x:c>
+      <x:c r="Q15" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>49</x:v>
@@ -1810,10 +1891,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>17</x:v>
@@ -1825,25 +1906,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M16" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q16" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P16" s="0">
+        <x:v>47274</x:v>
+      </x:c>
+      <x:c r="Q16" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>49</x:v>
@@ -1866,10 +1947,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
@@ -1881,25 +1962,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q17" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P17" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q17" s="0">
+        <x:v>47274</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>49</x:v>
@@ -1922,10 +2003,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>17</x:v>
@@ -1937,25 +2018,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P18" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q18" s="0">
+        <x:v>47274</x:v>
       </x:c>
       <x:c r="R18" s="2" t="s">
         <x:v>49</x:v>
@@ -1978,10 +2059,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
@@ -1993,25 +2074,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P19" s="0">
+        <x:v>47274</x:v>
+      </x:c>
+      <x:c r="Q19" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R19" s="2" t="s">
         <x:v>49</x:v>
@@ -2034,10 +2115,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
@@ -2049,28 +2130,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R20" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="P20" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q20" s="0">
+        <x:v>47274</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2090,10 +2171,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
@@ -2105,25 +2186,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q21" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P21" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q21" s="0">
+        <x:v>47274</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>49</x:v>
@@ -2146,10 +2227,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
@@ -2161,28 +2242,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R22" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="P22" s="0">
+        <x:v>47274</x:v>
+      </x:c>
+      <x:c r="Q22" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2202,43 +2283,2787 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R23" s="4" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:18">
+      <x:c r="A24" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M24" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P24" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="Q24" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R24" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:18">
+      <x:c r="A25" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G23" s="0" t="s">
+      <x:c r="L25" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
+      <x:c r="M25" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P25" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q25" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="R25" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:18">
+      <x:c r="A26" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M26" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N26" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O26" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P26" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="Q26" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R26" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:18">
+      <x:c r="A27" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M27" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P27" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q27" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="R27" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:18">
+      <x:c r="A28" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K28" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M28" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O28" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P28" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q28" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="R28" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:18">
+      <x:c r="A29" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L29" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M29" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P29" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="Q29" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R29" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:18">
+      <x:c r="A30" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L30" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M30" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P30" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q30" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="R30" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:18">
+      <x:c r="A31" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M31" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N31" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P31" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="Q31" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R31" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:18">
+      <x:c r="A32" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L32" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M32" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P32" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q32" s="0">
+        <x:v>44462</x:v>
+      </x:c>
+      <x:c r="R32" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:18">
+      <x:c r="A33" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L33" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R23" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="M33" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P33" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="Q33" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R33" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:18">
+      <x:c r="A34" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M34" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N34" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P34" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q34" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="R34" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:18">
+      <x:c r="A35" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M35" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N35" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P35" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="Q35" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R35" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:18">
+      <x:c r="A36" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L36" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M36" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N36" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O36" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P36" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="Q36" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R36" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:18">
+      <x:c r="A37" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L37" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M37" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P37" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q37" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="R37" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:18">
+      <x:c r="A38" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L38" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M38" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N38" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O38" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P38" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q38" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="R38" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:18">
+      <x:c r="A39" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L39" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M39" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N39" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P39" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="Q39" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R39" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:18">
+      <x:c r="A40" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L40" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M40" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N40" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P40" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q40" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="R40" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:18">
+      <x:c r="A41" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L41" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M41" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P41" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="Q41" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R41" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:18">
+      <x:c r="A42" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L42" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M42" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N42" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O42" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P42" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q42" s="0">
+        <x:v>51266</x:v>
+      </x:c>
+      <x:c r="R42" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:18">
+      <x:c r="A43" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L43" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M43" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P43" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="Q43" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R43" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:18">
+      <x:c r="A44" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L44" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N44" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O44" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P44" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q44" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="R44" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:18">
+      <x:c r="A45" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L45" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M45" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P45" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="Q45" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R45" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:18">
+      <x:c r="A46" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K46" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L46" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M46" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N46" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O46" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P46" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="Q46" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R46" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:18">
+      <x:c r="A47" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K47" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L47" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M47" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N47" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O47" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P47" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q47" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="R47" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:18">
+      <x:c r="A48" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L48" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M48" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N48" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O48" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="P48" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q48" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="R48" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:18">
+      <x:c r="A49" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K49" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L49" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M49" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N49" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P49" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="Q49" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R49" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:18">
+      <x:c r="A50" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K50" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L50" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M50" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N50" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P50" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q50" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="R50" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:18">
+      <x:c r="A51" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K51" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L51" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M51" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N51" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P51" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="Q51" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R51" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:18">
+      <x:c r="A52" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K52" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L52" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M52" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N52" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P52" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q52" s="0">
+        <x:v>47666</x:v>
+      </x:c>
+      <x:c r="R52" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:18">
+      <x:c r="A53" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L53" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M53" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N53" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O53" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P53" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="Q53" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R53" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:18">
+      <x:c r="A54" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K54" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L54" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M54" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N54" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O54" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P54" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q54" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="R54" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:18">
+      <x:c r="A55" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K55" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L55" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M55" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N55" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O55" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P55" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="Q55" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R55" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:18">
+      <x:c r="A56" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J56" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L56" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M56" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N56" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O56" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P56" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="Q56" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R56" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:18">
+      <x:c r="A57" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K57" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L57" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M57" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N57" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O57" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P57" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q57" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="R57" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:18">
+      <x:c r="A58" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J58" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K58" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L58" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M58" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N58" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O58" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="P58" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q58" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="R58" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:18">
+      <x:c r="A59" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K59" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L59" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M59" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N59" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O59" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P59" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="Q59" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R59" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:18">
+      <x:c r="A60" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K60" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L60" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M60" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N60" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O60" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P60" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q60" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="R60" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:18">
+      <x:c r="A61" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L61" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M61" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N61" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O61" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P61" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="Q61" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R61" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:18">
+      <x:c r="A62" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K62" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L62" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M62" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N62" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O62" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P62" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q62" s="0">
+        <x:v>38868</x:v>
+      </x:c>
+      <x:c r="R62" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:18">
+      <x:c r="A63" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K63" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L63" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M63" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N63" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O63" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P63" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="Q63" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R63" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:18">
+      <x:c r="A64" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L64" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M64" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N64" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O64" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P64" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q64" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="R64" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:18">
+      <x:c r="A65" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L65" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M65" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N65" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O65" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P65" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="Q65" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R65" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:18">
+      <x:c r="A66" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K66" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L66" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M66" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N66" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O66" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P66" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="Q66" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R66" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:18">
+      <x:c r="A67" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K67" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L67" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M67" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N67" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O67" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P67" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q67" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="R67" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:18">
+      <x:c r="A68" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J68" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K68" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L68" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M68" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N68" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O68" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P68" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q68" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="R68" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:18">
+      <x:c r="A69" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K69" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L69" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M69" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N69" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O69" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P69" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="Q69" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R69" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:18">
+      <x:c r="A70" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K70" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L70" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M70" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N70" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O70" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P70" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q70" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="R70" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:18">
+      <x:c r="A71" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K71" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L71" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M71" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N71" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O71" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P71" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="Q71" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R71" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:18">
+      <x:c r="A72" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K72" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L72" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M72" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N72" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O72" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P72" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q72" s="0">
+        <x:v>52734</x:v>
+      </x:c>
+      <x:c r="R72" s="5" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
